--- a/published/02_Grants_Active.xlsx
+++ b/published/02_Grants_Active.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Active_Grants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$H$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -55,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,19 +60,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -444,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -454,6 +445,7 @@
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,78 +484,93 @@
           <t>Source</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
+          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Lump sum of €4,000 (80% aid intensity)</t>
+          <t>Up to $500,000 CAD</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
+          <t>Aging, Brain Health, Healthcare Innovation</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
+          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-to-support-smes-business-reports-and-plans-malta/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/submissions-open-for-cabhis-fuel-program-in-canada/</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding for Agri-Food SME Value Chain Development (Moldova)</t>
+          <t>Grant Opportunity: Bold Woman Award for Women Entrepreneurs (South Africa)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>European Union (Managed by Solidarity Fund PL in Moldova)</t>
+          <t>Bold Open Database</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Maximum EUR 50,000 per project (Total budget EUR 250,000)</t>
+          <t>Award/Prize (Amount unspecified)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Agri-food value chain, cooperation and association, seed sector, organic farming</t>
+          <t>Women Entrepreneurs, Leadership, Business Success</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://eu4moldova.eu/en/grants-of-up-to-e50000-for-agricultural-producers-in-republica-moldova/</t>
+          <t>https://www.boldopendatabase.com/en/bold-woman-award</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-for-agri-food-sme-value-chain-development-moldova/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/bold-woman-award-for-women-entrepreneurs-south-africa/</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
@@ -603,11 +610,16 @@
           <t>https://fundsforcompanies.fundsforngos.org/grant/apply-now-funding-for-consolidated-research-infrastructure-clusters/</t>
         </is>
       </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
+          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -622,325 +634,370 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
+          <t>Maximum €10,000</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
+          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
+          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-standards-and-awards-support-for-smes-malta/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-marketing-strategy-support-grant-for-smes-malta/</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
+          <t>Grant Opportunity: Grants for Developing Internationalisation Strategies for SMEs (Malta)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Australian Government (Queensland)</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Up to $100,000</t>
+          <t>Maximum €20,000 per undertaking</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
+          <t>International market readiness, market feasibility, entry strategy, smart economic transformation</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
+          <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-private-sector-pathways-program-australia/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/grants-for-developing-internationalisation-strategies-for-smes-malta/</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Bold Woman Award for Women Entrepreneurs (South Africa)</t>
+          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bold Open Database</t>
+          <t>The Bridge Youth Resource Centre</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Award/Prize (Amount unspecified)</t>
+          <t>Up to $20,000 (Scholarship/Awards)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs, Leadership, Business Success</t>
+          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.boldopendatabase.com/en/bold-woman-award</t>
+          <t>https://thebridgeyouth.ca/take-your-shot/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/bold-woman-award-for-women-entrepreneurs-south-africa/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/cat/take-your-shot-program-entrepreneurship-program-canada/</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
+          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Whangārei District Council</t>
+          <t>European Space Agency (ESA)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
+          <t>Up to €75,000 per activity (75% of total project cost)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
+          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
+          <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-waste-minimisation-fund-in-new-zealand/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-call-for-space-tech-wetland-sustainability-projects/</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Grant Opportunity: AI Innovation Challenge to Transform Water Systems</t>
+          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Water Council</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Not specified (Innovation Challenge)</t>
+          <t>Lump sum of €4,000 (80% aid intensity)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI, Water Systems, Cognitive Water Ecosystem, Resource Stewardship</t>
+          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://thewatercouncil.com/open-innovation-programs/</t>
+          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/apply-for-ai-innovation-challenge-to-transform-water-systems/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-to-support-smes-business-reports-and-plans-malta/</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
+          <t>Grant Opportunity: AI Innovation Challenge to Transform Water Systems</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
+          <t>The Water Council</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Up to $500,000 CAD</t>
+          <t>Not specified (Innovation Challenge)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Aging, Brain Health, Healthcare Innovation</t>
+          <t>AI, Water Systems, Cognitive Water Ecosystem, Resource Stewardship</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
+          <t>https://thewatercouncil.com/open-innovation-programs/</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/submissions-open-for-cabhis-fuel-program-in-canada/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/apply-for-ai-innovation-challenge-to-transform-water-systems/</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
+          <t>Grant Opportunity: Funding for Agri-Food SME Value Chain Development (Moldova)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
+          <t>European Union (Managed by Solidarity Fund PL in Moldova)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$500,000 to $10 million</t>
+          <t>Maximum EUR 50,000 per project (Total budget EUR 250,000)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
+          <t>Agri-food value chain, cooperation and association, seed sector, organic farming</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
+          <t>https://eu4moldova.eu/en/grants-of-up-to-e50000-for-agricultural-producers-in-republica-moldova/</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-for-low-emissions-industry-program-in-australia/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-for-agri-food-sme-value-chain-development-moldova/</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
+          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cyber Valley</t>
+          <t>Whangārei District Council</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Not specified (Incubator program with practical platform and expertise)</t>
+          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
+          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://ai-incubator.is.mpg.de/</t>
+          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/training-and-mentorship/entries-open-for-cyber-valley-ai-incubator-program/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-waste-minimisation-fund-in-new-zealand/</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
+          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>European Space Agency (ESA)</t>
+          <t>Australian Government (Queensland)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Up to €75,000 per activity (75% of total project cost)</t>
+          <t>Up to $100,000</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
+          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
+          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-call-for-space-tech-wetland-sustainability-projects/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-private-sector-pathways-program-australia/</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
+          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -955,138 +1012,158 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Maximum €10,000</t>
+          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
+          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
+          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-marketing-strategy-support-grant-for-smes-malta/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-standards-and-awards-support-for-smes-malta/</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Grants for Developing Internationalisation Strategies for SMEs (Malta)</t>
+          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>Cyber Valley</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Maximum €20,000 per undertaking</t>
+          <t>Not specified (Incubator program with practical platform and expertise)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>International market readiness, market feasibility, entry strategy, smart economic transformation</t>
+          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
+          <t>https://ai-incubator.is.mpg.de/</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/grants-for-developing-internationalisation-strategies-for-smes-malta/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/training-and-mentorship/entries-open-for-cyber-valley-ai-incubator-program/</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
+          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>European Commission</t>
+          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
+          <t>$500,000 to $10 million</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
+          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
+          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-advancing-digital-twins-for-climate-environment-and-security/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-for-low-emissions-industry-program-in-australia/</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
+          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Bridge Youth Resource Centre</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Up to $20,000 (Scholarship/Awards)</t>
+          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
+          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://thebridgeyouth.ca/take-your-shot/</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/cat/take-your-shot-program-entrepreneurship-program-canada/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-advancing-digital-twins-for-climate-environment-and-security/</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/published/02_Grants_Active.xlsx
+++ b/published/02_Grants_Active.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +55,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,13 +63,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -493,37 +502,37 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
+          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Up to $500,000 CAD</t>
+          <t>Lump sum of €4,000 (80% aid intensity)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aging, Brain Health, Healthcare Innovation</t>
+          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
+          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/submissions-open-for-cabhis-fuel-program-in-canada/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-to-support-smes-business-reports-and-plans-malta/</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -535,37 +544,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Bold Woman Award for Women Entrepreneurs (South Africa)</t>
+          <t>Grant Opportunity: Funding for Agri-Food SME Value Chain Development (Moldova)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bold Open Database</t>
+          <t>European Union (Managed by Solidarity Fund PL in Moldova)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Award/Prize (Amount unspecified)</t>
+          <t>Maximum EUR 50,000 per project (Total budget EUR 250,000)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs, Leadership, Business Success</t>
+          <t>Agri-food value chain, cooperation and association, seed sector, organic farming</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.boldopendatabase.com/en/bold-woman-award</t>
+          <t>https://eu4moldova.eu/en/grants-of-up-to-e50000-for-agricultural-producers-in-republica-moldova/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/bold-woman-award-for-women-entrepreneurs-south-africa/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-for-agri-food-sme-value-chain-development-moldova/</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -619,7 +628,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
+          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -634,22 +643,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Maximum €10,000</t>
+          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
+          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
+          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-marketing-strategy-support-grant-for-smes-malta/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-standards-and-awards-support-for-smes-malta/</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -661,37 +670,37 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Grants for Developing Internationalisation Strategies for SMEs (Malta)</t>
+          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>Australian Government (Queensland)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Maximum €20,000 per undertaking</t>
+          <t>Up to $100,000</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>International market readiness, market feasibility, entry strategy, smart economic transformation</t>
+          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
+          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/grants-for-developing-internationalisation-strategies-for-smes-malta/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-private-sector-pathways-program-australia/</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -703,37 +712,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
+          <t>Grant Opportunity: Bold Woman Award for Women Entrepreneurs (South Africa)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Bridge Youth Resource Centre</t>
+          <t>Bold Open Database</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Up to $20,000 (Scholarship/Awards)</t>
+          <t>Award/Prize (Amount unspecified)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
+          <t>Women Entrepreneurs, Leadership, Business Success</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://thebridgeyouth.ca/take-your-shot/</t>
+          <t>https://www.boldopendatabase.com/en/bold-woman-award</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/cat/take-your-shot-program-entrepreneurship-program-canada/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/bold-woman-award-for-women-entrepreneurs-south-africa/</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -745,37 +754,37 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
+          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>European Space Agency (ESA)</t>
+          <t>Whangārei District Council</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Up to €75,000 per activity (75% of total project cost)</t>
+          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
+          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
+          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-call-for-space-tech-wetland-sustainability-projects/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-waste-minimisation-fund-in-new-zealand/</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -787,37 +796,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
+          <t>Grant Opportunity: AI Innovation Challenge to Transform Water Systems</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>The Water Council</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lump sum of €4,000 (80% aid intensity)</t>
+          <t>Not specified (Innovation Challenge)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
+          <t>AI, Water Systems, Cognitive Water Ecosystem, Resource Stewardship</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
+          <t>https://thewatercouncil.com/open-innovation-programs/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-to-support-smes-business-reports-and-plans-malta/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/apply-for-ai-innovation-challenge-to-transform-water-systems/</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -829,37 +838,37 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: AI Innovation Challenge to Transform Water Systems</t>
+          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>The Water Council</t>
+          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Not specified (Innovation Challenge)</t>
+          <t>Up to $500,000 CAD</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>AI, Water Systems, Cognitive Water Ecosystem, Resource Stewardship</t>
+          <t>Aging, Brain Health, Healthcare Innovation</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://thewatercouncil.com/open-innovation-programs/</t>
+          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/apply-for-ai-innovation-challenge-to-transform-water-systems/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/submissions-open-for-cabhis-fuel-program-in-canada/</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -871,37 +880,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding for Agri-Food SME Value Chain Development (Moldova)</t>
+          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>European Union (Managed by Solidarity Fund PL in Moldova)</t>
+          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Maximum EUR 50,000 per project (Total budget EUR 250,000)</t>
+          <t>$500,000 to $10 million</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Agri-food value chain, cooperation and association, seed sector, organic farming</t>
+          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://eu4moldova.eu/en/grants-of-up-to-e50000-for-agricultural-producers-in-republica-moldova/</t>
+          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-for-agri-food-sme-value-chain-development-moldova/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-for-low-emissions-industry-program-in-australia/</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -913,37 +922,37 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
+          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Whangārei District Council</t>
+          <t>Cyber Valley</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
+          <t>Not specified (Incubator program with practical platform and expertise)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
+          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
+          <t>https://ai-incubator.is.mpg.de/</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-waste-minimisation-fund-in-new-zealand/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/training-and-mentorship/entries-open-for-cyber-valley-ai-incubator-program/</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -955,37 +964,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
+          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Australian Government (Queensland)</t>
+          <t>European Space Agency (ESA)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Up to $100,000</t>
+          <t>Up to €75,000 per activity (75% of total project cost)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
+          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
+          <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-private-sector-pathways-program-australia/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-call-for-space-tech-wetland-sustainability-projects/</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -997,7 +1006,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
+          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1012,22 +1021,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
+          <t>Maximum €10,000</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
+          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
+          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-standards-and-awards-support-for-smes-malta/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-marketing-strategy-support-grant-for-smes-malta/</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1039,37 +1048,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
+          <t>Grant Opportunity: Grants for Developing Internationalisation Strategies for SMEs (Malta)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cyber Valley</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Not specified (Incubator program with practical platform and expertise)</t>
+          <t>Maximum €20,000 per undertaking</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
+          <t>International market readiness, market feasibility, entry strategy, smart economic transformation</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://ai-incubator.is.mpg.de/</t>
+          <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/training-and-mentorship/entries-open-for-cyber-valley-ai-incubator-program/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/grants-for-developing-internationalisation-strategies-for-smes-malta/</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1081,37 +1090,37 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
+          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$500,000 to $10 million</t>
+          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
+          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-for-low-emissions-industry-program-in-australia/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-advancing-digital-twins-for-climate-environment-and-security/</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1123,37 +1132,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
+          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>European Commission</t>
+          <t>The Bridge Youth Resource Centre</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
+          <t>Up to $20,000 (Scholarship/Awards)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
+          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
+          <t>https://thebridgeyouth.ca/take-your-shot/</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-advancing-digital-twins-for-climate-environment-and-security/</t>
+          <t>https://fundsforcompanies.fundsforngos.org/cat/take-your-shot-program-entrepreneurship-program-canada/</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">

--- a/published/02_Grants_Active.xlsx
+++ b/published/02_Grants_Active.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Active_Grants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -55,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,19 +60,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -444,17 +435,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,35 +457,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Focus Area</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Apply Link</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -502,40 +499,45 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
+          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>The Centre for Aging + Brain Health Innovation is accepting applications for its Fuel program, designed to remove barriers and accelerate innovative solutions that have the potential to transform the aging experience. The program supports start-up companies and healthcare/research organizations in advancing innovations and achieving validation milestones.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Lump sum of €4,000 (80% aid intensity)</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
+          <t>Up to $500,000 CAD</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
+          <t>Aging, Brain Health, Healthcare Innovation</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-to-support-smes-business-reports-and-plans-malta/</t>
+          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/submissions-open-for-cabhis-fuel-program-in-canada/</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -544,40 +546,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding for Agri-Food SME Value Chain Development (Moldova)</t>
+          <t>Grant Opportunity: Bold Woman Award for Women Entrepreneurs (South Africa)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>European Union (Managed by Solidarity Fund PL in Moldova)</t>
+          <t>The Bold Woman Award invites applications from women entrepreneurs to recognize their leadership, entrepreneurial journey, and business success. The awards focus on recognizing accomplished women entrepreneurs for their business achievements and leadership while also supporting emerging women entrepreneurs who have created or taken over a business within the past five years.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>Bold Open Database</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Maximum EUR 50,000 per project (Total budget EUR 250,000)</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Agri-food value chain, cooperation and association, seed sector, organic farming</t>
+          <t>Award/Prize (Amount unspecified)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://eu4moldova.eu/en/grants-of-up-to-e50000-for-agricultural-producers-in-republica-moldova/</t>
+          <t>Women Entrepreneurs, Leadership, Business Success</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-for-agri-food-sme-value-chain-development-moldova/</t>
+          <t>https://www.boldopendatabase.com/en/bold-woman-award</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/bold-woman-award-for-women-entrepreneurs-south-africa/</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -591,35 +598,40 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>The European Commission is advancing efforts to strengthen and streamline its research infrastructure ecosystem by supporting initiatives that improve coordination, accessibility, and policy engagement across large thematic domains. The programme aims to equip large thematic clusters of European research infrastructures with both a policy-oriented and a technical framework to better represent their collective interests and enhance collaboration across the research ecosystem.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>European Commission</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>€4,000,000 to €8,000,000 per project (Total budget: €40,000,000)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Research Infrastructure, Policy Engagement, Technological Framework, Innovation</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-DEV-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://fundsforcompanies.fundsforngos.org/grant/apply-now-funding-for-consolidated-research-infrastructure-clusters/</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -628,40 +640,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
+          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>The Marketing Strategy for Micro &amp; Small Enterprises scheme supports micro and small businesses in obtaining professional guidance to design marketing strategies that boost their competitiveness and drive business growth. It part-finances costs incurred for external services contracted to deliver a marketing strategy aligned with the enterprise’s objectives.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
+          <t>Maximum €10,000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
+          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-standards-and-awards-support-for-smes-malta/</t>
+          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-marketing-strategy-support-grant-for-smes-malta/</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -670,40 +687,45 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
+          <t>Grant Opportunity: Grants for Developing Internationalisation Strategies for SMEs (Malta)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Australian Government (Queensland)</t>
+          <t>The Internationalisation Strategy for SMEs scheme helps SMEs access expert support in developing strategies to improve efficiency, competitiveness, and international market readiness. The scheme supports studying opportunities abroad and developing strategies for selected countries, including marketing and sales plans and risk assessment.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Up to $100,000</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
+          <t>Maximum €20,000 per undertaking</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
+          <t>International market readiness, market feasibility, entry strategy, smart economic transformation</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-private-sector-pathways-program-australia/</t>
+          <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/grants-for-developing-internationalisation-strategies-for-smes-malta/</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -712,40 +734,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Bold Woman Award for Women Entrepreneurs (South Africa)</t>
+          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bold Open Database</t>
+          <t>The Take Your Shot program is an entrepreneurship program inviting applications from young entrepreneurs to develop their business ideas with funding and professional mentorship. The program includes mandatory workshops and a final pitch event where participants can present their ideas to a panel of judges.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>The Bridge Youth Resource Centre</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Award/Prize (Amount unspecified)</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs, Leadership, Business Success</t>
+          <t>Up to $20,000 (Scholarship/Awards)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.boldopendatabase.com/en/bold-woman-award</t>
+          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/bold-woman-award-for-women-entrepreneurs-south-africa/</t>
+          <t>https://thebridgeyouth.ca/take-your-shot/</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>https://fundsforcompanies.fundsforngos.org/cat/take-your-shot-program-entrepreneurship-program-canada/</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -754,40 +781,45 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
+          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Whangārei District Council</t>
+          <t>The European Space Agency is seeking applications to develop space-enabled applications that support wetland sustainability and create viable business opportunities. The opportunity supports feasibility studies over a six-month period for early-stage service concepts that respond to real customer needs while demonstrating technical feasibility and commercial potential.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>European Space Agency (ESA)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
+          <t>Up to €75,000 per activity (75% of total project cost)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
+          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-waste-minimisation-fund-in-new-zealand/</t>
+          <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-call-for-space-tech-wetland-sustainability-projects/</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -796,40 +828,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Grant Opportunity: AI Innovation Challenge to Transform Water Systems</t>
+          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Water Council</t>
+          <t>The Business Reports for SMEs Grant Scheme offers funding to support SMEs in creating external consultancy reports to improve efficiency, competitiveness, and investment readiness. It provides financial support to contract external expertise needed to generate high-quality business reports that inform strategic decisions and strengthen operational performance.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Not specified (Innovation Challenge)</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI, Water Systems, Cognitive Water Ecosystem, Resource Stewardship</t>
+          <t>Lump sum of €4,000 (80% aid intensity)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://thewatercouncil.com/open-innovation-programs/</t>
+          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/apply-for-ai-innovation-challenge-to-transform-water-systems/</t>
+          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-to-support-smes-business-reports-and-plans-malta/</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -838,40 +875,45 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
+          <t>Grant Opportunity: AI Innovation Challenge to Transform Water Systems</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
+          <t>The Water Council is seeking innovative AI-native technologies that can strengthen how water systems are sensed, treated, moved, recovered, and managed to build a more reliable and sustainable water ecosystem. The challenge focuses on developing AI-native components for a cognitive water ecosystem, advancing molecular intelligence, enabling autonomous infrastructure, and improving resource stewardship.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>The Water Council</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Up to $500,000 CAD</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Aging, Brain Health, Healthcare Innovation</t>
+          <t>Not specified (Innovation Challenge)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
+          <t>AI, Water Systems, Cognitive Water Ecosystem, Resource Stewardship</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/submissions-open-for-cabhis-fuel-program-in-canada/</t>
+          <t>https://thewatercouncil.com/open-innovation-programs/</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/apply-for-ai-innovation-challenge-to-transform-water-systems/</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -880,40 +922,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
+          <t>Grant Opportunity: Funding for Agri-Food SME Value Chain Development (Moldova)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
+          <t>The European Union is seeking grant applications to support the development of sustainable and competitive agri-food SMEs in the Republic of Moldova through strengthened cooperation and value chain initiatives. The call focuses on reducing economic fragmentation, optimizing costs, and supporting market integration and collective functioning.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>European Union (Managed by Solidarity Fund PL in Moldova)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$500,000 to $10 million</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
+          <t>Maximum EUR 50,000 per project (Total budget EUR 250,000)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
+          <t>Agri-food value chain, cooperation and association, seed sector, organic farming</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-for-low-emissions-industry-program-in-australia/</t>
+          <t>https://eu4moldova.eu/en/grants-of-up-to-e50000-for-agricultural-producers-in-republica-moldova/</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-for-agri-food-sme-value-chain-development-moldova/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -922,40 +969,45 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
+          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cyber Valley</t>
+          <t>The Waste Minimisation Fund is seeking applications to support innovative projects that reduce waste, improve resource efficiency, and encourage community participation, education, and long-term behaviour change across the Whangārei District. The fund focuses on complementing and enhancing existing waste minimisation programmes and creating new opportunities for reducing waste.</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>Whangārei District Council</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Not specified (Incubator program with practical platform and expertise)</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
+          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://ai-incubator.is.mpg.de/</t>
+          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/training-and-mentorship/entries-open-for-cyber-valley-ai-incubator-program/</t>
+          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-waste-minimisation-fund-in-new-zealand/</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -964,40 +1016,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
+          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>European Space Agency (ESA)</t>
+          <t>The Private Sector Pathways Program is inviting applications to support innovative small-to-medium enterprises in Queensland to collaborate with corporate partners and develop commercialisation opportunities. The program focuses on increasing partnerships between SMEs and corporate businesses or large organisations to solve problems and trial technologies.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>Australian Government (Queensland)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Up to €75,000 per activity (75% of total project cost)</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
+          <t>Up to $100,000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
+          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-call-for-space-tech-wetland-sustainability-projects/</t>
+          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-private-sector-pathways-program-australia/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -1006,40 +1063,45 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
+          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>The Standards &amp; Awards for SMEs scheme assists small and medium-sized enterprises in strengthening their business operations and attaining prestigious national or international standards and awards. The scheme focuses on enhancing competitiveness and credibility through internationally recognized certifications or national excellence awards.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Maximum €10,000</t>
-        </is>
-      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
+          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
+          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-marketing-strategy-support-grant-for-smes-malta/</t>
+          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-standards-and-awards-support-for-smes-malta/</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -1048,40 +1110,45 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Grants for Developing Internationalisation Strategies for SMEs (Malta)</t>
+          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>The Cyber Valley AI Incubator offers a practical platform for researchers, technologists, and innovators to develop and launch AI-driven ventures. The program provides a collaborative environment where participants can develop their ideas into tangible ventures, leveraging world-class research and expertise.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>Cyber Valley</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Maximum €20,000 per undertaking</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>International market readiness, market feasibility, entry strategy, smart economic transformation</t>
+          <t>Not specified (Incubator program with practical platform and expertise)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
+          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/grants-for-developing-internationalisation-strategies-for-smes-malta/</t>
+          <t>https://ai-incubator.is.mpg.de/</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
+        <is>
+          <t>https://fundsforcompanies.fundsforngos.org/training-and-mentorship/entries-open-for-cyber-valley-ai-incubator-program/</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -1090,40 +1157,45 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
+          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>European Commission</t>
+          <t>The Low Emissions Industry Program supports projects that reduce emissions in mining and manufacturing facilities while strengthening their transition toward a low-carbon future. The program focuses on driving emissions reductions by co-funding projects, future-proofing industrial assets, and maintaining economic resilience.</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
+          <t>$500,000 to $10 million</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
+          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-advancing-digital-twins-for-climate-environment-and-security/</t>
+          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-for-low-emissions-industry-program-in-australia/</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -1132,47 +1204,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
+          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Bridge Youth Resource Centre</t>
+          <t>The European Commission is supporting initiatives to develop advanced digital twin technologies that strengthen preparedness, resilience and decision-making in response to the growing security challenges linked to climate and environmental change. The initiative focuses on improving security and preparedness for the Union and creating a more disaster-resilient society in the face of climate change impacts.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Up to $20,000 (Scholarship/Awards)</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
+          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://thebridgeyouth.ca/take-your-shot/</t>
+          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/cat/take-your-shot-program-entrepreneurship-program-canada/</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-advancing-digital-twins-for-climate-environment-and-security/</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>VERIFIED</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:I17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/published/02_Grants_Active.xlsx
+++ b/published/02_Grants_Active.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Active_Grants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$G$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -445,8 +445,6 @@
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,16 +483,6 @@
           <t>Apply Link</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -532,16 +520,6 @@
           <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/submissions-open-for-cabhis-fuel-program-in-canada/</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -579,16 +557,6 @@
           <t>https://www.boldopendatabase.com/en/bold-woman-award</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/bold-woman-award-for-women-entrepreneurs-south-africa/</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -626,16 +594,6 @@
           <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-DEV-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/apply-now-funding-for-consolidated-research-infrastructure-clusters/</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -673,16 +631,6 @@
           <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-marketing-strategy-support-grant-for-smes-malta/</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -720,16 +668,6 @@
           <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/grants-for-developing-internationalisation-strategies-for-smes-malta/</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -767,16 +705,6 @@
           <t>https://thebridgeyouth.ca/take-your-shot/</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/cat/take-your-shot-program-entrepreneurship-program-canada/</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -814,16 +742,6 @@
           <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-call-for-space-tech-wetland-sustainability-projects/</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -861,395 +779,231 @@
           <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-to-support-smes-business-reports-and-plans-malta/</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: AI Innovation Challenge to Transform Water Systems</t>
+          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>The Water Council is seeking innovative AI-native technologies that can strengthen how water systems are sensed, treated, moved, recovered, and managed to build a more reliable and sustainable water ecosystem. The challenge focuses on developing AI-native components for a cognitive water ecosystem, advancing molecular intelligence, enabling autonomous infrastructure, and improving resource stewardship.</t>
+          <t>The Waste Minimisation Fund is seeking applications to support innovative projects that reduce waste, improve resource efficiency, and encourage community participation, education, and long-term behaviour change across the Whangārei District. The fund focuses on complementing and enhancing existing waste minimisation programmes and creating new opportunities for reducing waste.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The Water Council</t>
+          <t>Whangārei District Council</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Not specified (Innovation Challenge)</t>
+          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>AI, Water Systems, Cognitive Water Ecosystem, Resource Stewardship</t>
+          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://thewatercouncil.com/open-innovation-programs/</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/apply-for-ai-innovation-challenge-to-transform-water-systems/</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding for Agri-Food SME Value Chain Development (Moldova)</t>
+          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The European Union is seeking grant applications to support the development of sustainable and competitive agri-food SMEs in the Republic of Moldova through strengthened cooperation and value chain initiatives. The call focuses on reducing economic fragmentation, optimizing costs, and supporting market integration and collective functioning.</t>
+          <t>The Private Sector Pathways Program is inviting applications to support innovative small-to-medium enterprises in Queensland to collaborate with corporate partners and develop commercialisation opportunities. The program focuses on increasing partnerships between SMEs and corporate businesses or large organisations to solve problems and trial technologies.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>European Union (Managed by Solidarity Fund PL in Moldova)</t>
+          <t>Australian Government (Queensland)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maximum EUR 50,000 per project (Total budget EUR 250,000)</t>
+          <t>Up to $100,000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Agri-food value chain, cooperation and association, seed sector, organic farming</t>
+          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://eu4moldova.eu/en/grants-of-up-to-e50000-for-agricultural-producers-in-republica-moldova/</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-for-agri-food-sme-value-chain-development-moldova/</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
+          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>The Waste Minimisation Fund is seeking applications to support innovative projects that reduce waste, improve resource efficiency, and encourage community participation, education, and long-term behaviour change across the Whangārei District. The fund focuses on complementing and enhancing existing waste minimisation programmes and creating new opportunities for reducing waste.</t>
+          <t>The Standards &amp; Awards for SMEs scheme assists small and medium-sized enterprises in strengthening their business operations and attaining prestigious national or international standards and awards. The scheme focuses on enhancing competitiveness and credibility through internationally recognized certifications or national excellence awards.</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Whangārei District Council</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
+          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
+          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-waste-minimisation-fund-in-new-zealand/</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
+          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Private Sector Pathways Program is inviting applications to support innovative small-to-medium enterprises in Queensland to collaborate with corporate partners and develop commercialisation opportunities. The program focuses on increasing partnerships between SMEs and corporate businesses or large organisations to solve problems and trial technologies.</t>
+          <t>The Cyber Valley AI Incubator offers a practical platform for researchers, technologists, and innovators to develop and launch AI-driven ventures. The program provides a collaborative environment where participants can develop their ideas into tangible ventures, leveraging world-class research and expertise.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Australian Government (Queensland)</t>
+          <t>Cyber Valley</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Up to $100,000</t>
+          <t>Not specified (Incubator program with practical platform and expertise)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
+          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-private-sector-pathways-program-australia/</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://ai-incubator.is.mpg.de/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
+          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>The Standards &amp; Awards for SMEs scheme assists small and medium-sized enterprises in strengthening their business operations and attaining prestigious national or international standards and awards. The scheme focuses on enhancing competitiveness and credibility through internationally recognized certifications or national excellence awards.</t>
+          <t>The Low Emissions Industry Program supports projects that reduce emissions in mining and manufacturing facilities while strengthening their transition toward a low-carbon future. The program focuses on driving emissions reductions by co-funding projects, future-proofing industrial assets, and maintaining economic resilience.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
+          <t>$500,000 to $10 million</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
+          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-standards-and-awards-support-for-smes-malta/</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
+          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Cyber Valley AI Incubator offers a practical platform for researchers, technologists, and innovators to develop and launch AI-driven ventures. The program provides a collaborative environment where participants can develop their ideas into tangible ventures, leveraging world-class research and expertise.</t>
+          <t>The European Commission is supporting initiatives to develop advanced digital twin technologies that strengthen preparedness, resilience and decision-making in response to the growing security challenges linked to climate and environmental change. The initiative focuses on improving security and preparedness for the Union and creating a more disaster-resilient society in the face of climate change impacts.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyber Valley</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Not specified (Incubator program with practical platform and expertise)</t>
+          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
+          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://ai-incubator.is.mpg.de/</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/training-and-mentorship/entries-open-for-cyber-valley-ai-incubator-program/</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>The Low Emissions Industry Program supports projects that reduce emissions in mining and manufacturing facilities while strengthening their transition toward a low-carbon future. The program focuses on driving emissions reductions by co-funding projects, future-proofing industrial assets, and maintaining economic resilience.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>$500,000 to $10 million</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-for-low-emissions-industry-program-in-australia/</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>The European Commission is supporting initiatives to develop advanced digital twin technologies that strengthen preparedness, resilience and decision-making in response to the growing security challenges linked to climate and environmental change. The initiative focuses on improving security and preparedness for the Union and creating a more disaster-resilient society in the face of climate change impacts.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>European Commission</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
           <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-advancing-digital-twins-for-climate-environment-and-security/</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I17"/>
+  <autoFilter ref="A1:G15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/published/02_Grants_Active.xlsx
+++ b/published/02_Grants_Active.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Active_Grants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$G$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -55,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,19 +60,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -444,17 +435,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,121 +455,106 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Focus Area</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Apply Link</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
+          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>The Centre for Aging + Brain Health Innovation is accepting applications for its Fuel program, designed to remove barriers and accelerate innovative solutions that have the potential to transform the aging experience. The program supports start-up companies and healthcare/research organizations in advancing innovations and achieving validation milestones.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Lump sum of €4,000 (80% aid intensity)</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
+          <t>Up to $500,000 CAD</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
+          <t>Aging, Brain Health, Healthcare Innovation</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-to-support-smes-business-reports-and-plans-malta/</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding for Agri-Food SME Value Chain Development (Moldova)</t>
+          <t>Grant Opportunity: Bold Woman Award for Women Entrepreneurs (South Africa)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>European Union (Managed by Solidarity Fund PL in Moldova)</t>
+          <t>The Bold Woman Award invites applications from women entrepreneurs to recognize their leadership, entrepreneurial journey, and business success. The awards focus on recognizing accomplished women entrepreneurs for their business achievements and leadership while also supporting emerging women entrepreneurs who have created or taken over a business within the past five years.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>Bold Open Database</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Maximum EUR 50,000 per project (Total budget EUR 250,000)</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Agri-food value chain, cooperation and association, seed sector, organic farming</t>
+          <t>Award/Prize (Amount unspecified)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://eu4moldova.eu/en/grants-of-up-to-e50000-for-agricultural-producers-in-republica-moldova/</t>
+          <t>Women Entrepreneurs, Leadership, Business Success</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-for-agri-food-sme-value-chain-development-moldova/</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://www.boldopendatabase.com/en/bold-woman-award</t>
         </is>
       </c>
     </row>
@@ -591,588 +566,444 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>The European Commission is advancing efforts to strengthen and streamline its research infrastructure ecosystem by supporting initiatives that improve coordination, accessibility, and policy engagement across large thematic domains. The programme aims to equip large thematic clusters of European research infrastructures with both a policy-oriented and a technical framework to better represent their collective interests and enhance collaboration across the research ecosystem.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>European Commission</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>€4,000,000 to €8,000,000 per project (Total budget: €40,000,000)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Research Infrastructure, Policy Engagement, Technological Framework, Innovation</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-DEV-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/apply-now-funding-for-consolidated-research-infrastructure-clusters/</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
+          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>The Marketing Strategy for Micro &amp; Small Enterprises scheme supports micro and small businesses in obtaining professional guidance to design marketing strategies that boost their competitiveness and drive business growth. It part-finances costs incurred for external services contracted to deliver a marketing strategy aligned with the enterprise’s objectives.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
+          <t>Maximum €10,000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
+          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-standards-and-awards-support-for-smes-malta/</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
+          <t>Grant Opportunity: Grants for Developing Internationalisation Strategies for SMEs (Malta)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Australian Government (Queensland)</t>
+          <t>The Internationalisation Strategy for SMEs scheme helps SMEs access expert support in developing strategies to improve efficiency, competitiveness, and international market readiness. The scheme supports studying opportunities abroad and developing strategies for selected countries, including marketing and sales plans and risk assessment.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Up to $100,000</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
+          <t>Maximum €20,000 per undertaking</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
+          <t>International market readiness, market feasibility, entry strategy, smart economic transformation</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-private-sector-pathways-program-australia/</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Bold Woman Award for Women Entrepreneurs (South Africa)</t>
+          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bold Open Database</t>
+          <t>The Take Your Shot program is an entrepreneurship program inviting applications from young entrepreneurs to develop their business ideas with funding and professional mentorship. The program includes mandatory workshops and a final pitch event where participants can present their ideas to a panel of judges.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>The Bridge Youth Resource Centre</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Award/Prize (Amount unspecified)</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs, Leadership, Business Success</t>
+          <t>Up to $20,000 (Scholarship/Awards)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.boldopendatabase.com/en/bold-woman-award</t>
+          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/bold-woman-award-for-women-entrepreneurs-south-africa/</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://thebridgeyouth.ca/take-your-shot/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
+          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Whangārei District Council</t>
+          <t>The European Space Agency is seeking applications to develop space-enabled applications that support wetland sustainability and create viable business opportunities. The opportunity supports feasibility studies over a six-month period for early-stage service concepts that respond to real customer needs while demonstrating technical feasibility and commercial potential.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>European Space Agency (ESA)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
+          <t>Up to €75,000 per activity (75% of total project cost)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
+          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/applications-open-for-waste-minimisation-fund-in-new-zealand/</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Grant Opportunity: AI Innovation Challenge to Transform Water Systems</t>
+          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Water Council</t>
+          <t>The Business Reports for SMEs Grant Scheme offers funding to support SMEs in creating external consultancy reports to improve efficiency, competitiveness, and investment readiness. It provides financial support to contract external expertise needed to generate high-quality business reports that inform strategic decisions and strengthen operational performance.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Not specified (Innovation Challenge)</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI, Water Systems, Cognitive Water Ecosystem, Resource Stewardship</t>
+          <t>Lump sum of €4,000 (80% aid intensity)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://thewatercouncil.com/open-innovation-programs/</t>
+          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/awards-and-prizes/apply-for-ai-innovation-challenge-to-transform-water-systems/</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
+          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
+          <t>The Waste Minimisation Fund is seeking applications to support innovative projects that reduce waste, improve resource efficiency, and encourage community participation, education, and long-term behaviour change across the Whangārei District. The fund focuses on complementing and enhancing existing waste minimisation programmes and creating new opportunities for reducing waste.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>Whangārei District Council</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Up to $500,000 CAD</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Aging, Brain Health, Healthcare Innovation</t>
+          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
+          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/submissions-open-for-cabhis-fuel-program-in-canada/</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
+          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
+          <t>The Private Sector Pathways Program is inviting applications to support innovative small-to-medium enterprises in Queensland to collaborate with corporate partners and develop commercialisation opportunities. The program focuses on increasing partnerships between SMEs and corporate businesses or large organisations to solve problems and trial technologies.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>Australian Government (Queensland)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>$500,000 to $10 million</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
+          <t>Up to $100,000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
+          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-for-low-emissions-industry-program-in-australia/</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
+          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cyber Valley</t>
+          <t>The Standards &amp; Awards for SMEs scheme assists small and medium-sized enterprises in strengthening their business operations and attaining prestigious national or international standards and awards. The scheme focuses on enhancing competitiveness and credibility through internationally recognized certifications or national excellence awards.</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Not specified (Incubator program with practical platform and expertise)</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
+          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>https://ai-incubator.is.mpg.de/</t>
+          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/training-and-mentorship/entries-open-for-cyber-valley-ai-incubator-program/</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
+          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>European Space Agency (ESA)</t>
+          <t>The Cyber Valley AI Incubator offers a practical platform for researchers, technologists, and innovators to develop and launch AI-driven ventures. The program provides a collaborative environment where participants can develop their ideas into tangible ventures, leveraging world-class research and expertise.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>Cyber Valley</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Up to €75,000 per activity (75% of total project cost)</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
+          <t>Not specified (Incubator program with practical platform and expertise)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
+          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/funding-call-for-space-tech-wetland-sustainability-projects/</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://ai-incubator.is.mpg.de/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
+          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>The Low Emissions Industry Program supports projects that reduce emissions in mining and manufacturing facilities while strengthening their transition toward a low-carbon future. The program focuses on driving emissions reductions by co-funding projects, future-proofing industrial assets, and maintaining economic resilience.</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Maximum €10,000</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
+          <t>$500,000 to $10 million</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
+          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/open-call-marketing-strategy-support-grant-for-smes-malta/</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
+          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Grants for Developing Internationalisation Strategies for SMEs (Malta)</t>
+          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>The European Commission is supporting initiatives to develop advanced digital twin technologies that strengthen preparedness, resilience and decision-making in response to the growing security challenges linked to climate and environmental change. The initiative focuses on improving security and preparedness for the Union and creating a more disaster-resilient society in the face of climate change impacts.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Maximum €20,000 per undertaking</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>International market readiness, market feasibility, entry strategy, smart economic transformation</t>
+          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
+          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/grants-for-developing-internationalisation-strategies-for-smes-malta/</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>European Commission</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
           <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/grant/cfas-advancing-digital-twins-for-climate-environment-and-security/</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>The Bridge Youth Resource Centre</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Up to $20,000 (Scholarship/Awards)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://thebridgeyouth.ca/take-your-shot/</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://fundsforcompanies.fundsforngos.org/cat/take-your-shot-program-entrepreneurship-program-canada/</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:G15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/published/02_Grants_Active.xlsx
+++ b/published/02_Grants_Active.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Active_Grants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +55,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,13 +63,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -435,575 +444,583 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Grant Title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Organization</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Focus Area</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Apply Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Grant Opportunity: Grants for Developing Internationalisation Strategies for SMEs (Malta)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>The Internationalisation Strategy for SMEs scheme helps SMEs access expert support in developing strategies to improve efficiency, competitiveness, and international market readiness. The scheme supports studying opportunities abroad and developing strategies for selected countries, including marketing and sales plans and risk assessment.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>FONDI.eu (Government of Malta)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Maximum €20,000 per undertaking</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>International market readiness, market feasibility, entry strategy, smart economic transformation</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>The Standards &amp; Awards for SMEs scheme assists small and medium-sized enterprises in strengthening their business operations and attaining prestigious national or international standards and awards. The scheme focuses on enhancing competitiveness and credibility through internationally recognized certifications or national excellence awards.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FONDI.eu (Government of Malta)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Grant Opportunity: Funding for Consolidated Research Infrastructure Clusters</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>The European Commission is advancing efforts to strengthen and streamline its research infrastructure ecosystem by supporting initiatives that improve coordination, accessibility, and policy engagement across large thematic domains. The programme aims to equip large thematic clusters of European research infrastructures with both a policy-oriented and a technical framework to better represent their collective interests and enhance collaboration across the research ecosystem.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>European Commission</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>€4,000,000 to €8,000,000 per project (Total budget: €40,000,000)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Research Infrastructure, Policy Engagement, Technological Framework, Innovation</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-DEV-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The Private Sector Pathways Program is inviting applications to support innovative small-to-medium enterprises in Queensland to collaborate with corporate partners and develop commercialisation opportunities. The program focuses on increasing partnerships between SMEs and corporate businesses or large organisations to solve problems and trial technologies.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Australian Government (Queensland)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Up to $100,000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>The Cyber Valley AI Incubator offers a practical platform for researchers, technologists, and innovators to develop and launch AI-driven ventures. The program provides a collaborative environment where participants can develop their ideas into tangible ventures, leveraging world-class research and expertise.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Cyber Valley</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Not specified (Incubator program with practical platform and expertise)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>https://ai-incubator.is.mpg.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The Low Emissions Industry Program supports projects that reduce emissions in mining and manufacturing facilities while strengthening their transition toward a low-carbon future. The program focuses on driving emissions reductions by co-funding projects, future-proofing industrial assets, and maintaining economic resilience.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>$500,000 to $10 million</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>The Waste Minimisation Fund is seeking applications to support innovative projects that reduce waste, improve resource efficiency, and encourage community participation, education, and long-term behaviour change across the Whangārei District. The fund focuses on complementing and enhancing existing waste minimisation programmes and creating new opportunities for reducing waste.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Whangārei District Council</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>The European Commission is supporting initiatives to develop advanced digital twin technologies that strengthen preparedness, resilience and decision-making in response to the growing security challenges linked to climate and environmental change. The initiative focuses on improving security and preparedness for the Union and creating a more disaster-resilient society in the face of climate change impacts.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>European Commission</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>The Take Your Shot program is an entrepreneurship program inviting applications from young entrepreneurs to develop their business ideas with funding and professional mentorship. The program includes mandatory workshops and a final pitch event where participants can present their ideas to a panel of judges.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>The Bridge Youth Resource Centre</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Up to $20,000 (Scholarship/Awards)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>https://thebridgeyouth.ca/take-your-shot/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>The Centre for Aging + Brain Health Innovation is accepting applications for its Fuel program, designed to remove barriers and accelerate innovative solutions that have the potential to transform the aging experience. The program supports start-up companies and healthcare/research organizations in advancing innovations and achieving validation milestones.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Up to $500,000 CAD</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Aging, Brain Health, Healthcare Innovation</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Bold Woman Award for Women Entrepreneurs (South Africa)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>The Bold Woman Award invites applications from women entrepreneurs to recognize their leadership, entrepreneurial journey, and business success. The awards focus on recognizing accomplished women entrepreneurs for their business achievements and leadership while also supporting emerging women entrepreneurs who have created or taken over a business within the past five years.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bold Open Database</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Award/Prize (Amount unspecified)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Women Entrepreneurs, Leadership, Business Success</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.boldopendatabase.com/en/bold-woman-award</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Funding for Consolidated Research Infrastructure Clusters</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>The European Commission is advancing efforts to strengthen and streamline its research infrastructure ecosystem by supporting initiatives that improve coordination, accessibility, and policy engagement across large thematic domains. The programme aims to equip large thematic clusters of European research infrastructures with both a policy-oriented and a technical framework to better represent their collective interests and enhance collaboration across the research ecosystem.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>European Commission</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>€4,000,000 to €8,000,000 per project (Total budget: €40,000,000)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Research Infrastructure, Policy Engagement, Technological Framework, Innovation</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-DEV-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>The Business Reports for SMEs Grant Scheme offers funding to support SMEs in creating external consultancy reports to improve efficiency, competitiveness, and investment readiness. It provides financial support to contract external expertise needed to generate high-quality business reports that inform strategic decisions and strengthen operational performance.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>FONDI.eu (Government of Malta)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Lump sum of €4,000 (80% aid intensity)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>The Marketing Strategy for Micro &amp; Small Enterprises scheme supports micro and small businesses in obtaining professional guidance to design marketing strategies that boost their competitiveness and drive business growth. It part-finances costs incurred for external services contracted to deliver a marketing strategy aligned with the enterprise’s objectives.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Maximum €10,000</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Grants for Developing Internationalisation Strategies for SMEs (Malta)</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>The Internationalisation Strategy for SMEs scheme helps SMEs access expert support in developing strategies to improve efficiency, competitiveness, and international market readiness. The scheme supports studying opportunities abroad and developing strategies for selected countries, including marketing and sales plans and risk assessment.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>FONDI.eu (Government of Malta)</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Maximum €20,000 per undertaking</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>International market readiness, market feasibility, entry strategy, smart economic transformation</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>The Take Your Shot program is an entrepreneurship program inviting applications from young entrepreneurs to develop their business ideas with funding and professional mentorship. The program includes mandatory workshops and a final pitch event where participants can present their ideas to a panel of judges.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>The Bridge Youth Resource Centre</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Up to $20,000 (Scholarship/Awards)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://thebridgeyouth.ca/take-your-shot/</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>The European Space Agency is seeking applications to develop space-enabled applications that support wetland sustainability and create viable business opportunities. The opportunity supports feasibility studies over a six-month period for early-stage service concepts that respond to real customer needs while demonstrating technical feasibility and commercial potential.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>European Space Agency (ESA)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Up to €75,000 per activity (75% of total project cost)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>The Business Reports for SMEs Grant Scheme offers funding to support SMEs in creating external consultancy reports to improve efficiency, competitiveness, and investment readiness. It provides financial support to contract external expertise needed to generate high-quality business reports that inform strategic decisions and strengthen operational performance.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>FONDI.eu (Government of Malta)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Lump sum of €4,000 (80% aid intensity)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>The Waste Minimisation Fund is seeking applications to support innovative projects that reduce waste, improve resource efficiency, and encourage community participation, education, and long-term behaviour change across the Whangārei District. The fund focuses on complementing and enhancing existing waste minimisation programmes and creating new opportunities for reducing waste.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Whangārei District Council</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>The Private Sector Pathways Program is inviting applications to support innovative small-to-medium enterprises in Queensland to collaborate with corporate partners and develop commercialisation opportunities. The program focuses on increasing partnerships between SMEs and corporate businesses or large organisations to solve problems and trial technologies.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Australian Government (Queensland)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Up to $100,000</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>The Standards &amp; Awards for SMEs scheme assists small and medium-sized enterprises in strengthening their business operations and attaining prestigious national or international standards and awards. The scheme focuses on enhancing competitiveness and credibility through internationally recognized certifications or national excellence awards.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>FONDI.eu (Government of Malta)</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>The Cyber Valley AI Incubator offers a practical platform for researchers, technologists, and innovators to develop and launch AI-driven ventures. The program provides a collaborative environment where participants can develop their ideas into tangible ventures, leveraging world-class research and expertise.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Cyber Valley</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Not specified (Incubator program with practical platform and expertise)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://ai-incubator.is.mpg.de/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>The Low Emissions Industry Program supports projects that reduce emissions in mining and manufacturing facilities while strengthening their transition toward a low-carbon future. The program focuses on driving emissions reductions by co-funding projects, future-proofing industrial assets, and maintaining economic resilience.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>$500,000 to $10 million</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>The European Commission is supporting initiatives to develop advanced digital twin technologies that strengthen preparedness, resilience and decision-making in response to the growing security challenges linked to climate and environmental change. The initiative focuses on improving security and preparedness for the Union and creating a more disaster-resilient society in the face of climate change impacts.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>European Commission</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:H14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/published/02_Grants_Active.xlsx
+++ b/published/02_Grants_Active.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Active_Grants" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active_Grants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$H$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -55,7 +52,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,19 +60,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -444,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -505,37 +496,37 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Grants for Developing Internationalisation Strategies for SMEs (Malta)</t>
+          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The Internationalisation Strategy for SMEs scheme helps SMEs access expert support in developing strategies to improve efficiency, competitiveness, and international market readiness. The scheme supports studying opportunities abroad and developing strategies for selected countries, including marketing and sales plans and risk assessment.</t>
+          <t>The Centre for Aging + Brain Health Innovation is accepting applications for its Fuel program, designed to remove barriers and accelerate innovative solutions that have the potential to transform the aging experience. The program supports start-up companies and healthcare/research organizations in advancing innovations and achieving validation milestones.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Maximum €20,000 per undertaking</t>
+          <t>Up to $500,000 CAD</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>International market readiness, market feasibility, entry strategy, smart economic transformation</t>
+          <t>Aging, Brain Health, Healthcare Innovation</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
+          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
         </is>
       </c>
     </row>
@@ -545,37 +536,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
+          <t>Grant Opportunity: Funding for Consolidated Research Infrastructure Clusters</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The Standards &amp; Awards for SMEs scheme assists small and medium-sized enterprises in strengthening their business operations and attaining prestigious national or international standards and awards. The scheme focuses on enhancing competitiveness and credibility through internationally recognized certifications or national excellence awards.</t>
+          <t>The European Commission is advancing efforts to strengthen and streamline its research infrastructure ecosystem by supporting initiatives that improve coordination, accessibility, and policy engagement across large thematic domains. The programme aims to equip large thematic clusters of European research infrastructures with both a policy-oriented and a technical framework to better represent their collective interests and enhance collaboration across the research ecosystem.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
+          <t>€4,000,000 to €8,000,000 per project (Total budget: €40,000,000)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
+          <t>Research Infrastructure, Policy Engagement, Technological Framework, Innovation</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-DEV-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
         </is>
       </c>
     </row>
@@ -585,37 +576,37 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding for Consolidated Research Infrastructure Clusters</t>
+          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The European Commission is advancing efforts to strengthen and streamline its research infrastructure ecosystem by supporting initiatives that improve coordination, accessibility, and policy engagement across large thematic domains. The programme aims to equip large thematic clusters of European research infrastructures with both a policy-oriented and a technical framework to better represent their collective interests and enhance collaboration across the research ecosystem.</t>
+          <t>The Marketing Strategy for Micro &amp; Small Enterprises scheme supports micro and small businesses in obtaining professional guidance to design marketing strategies that boost their competitiveness and drive business growth. It part-finances costs incurred for external services contracted to deliver a marketing strategy aligned with the enterprise’s objectives.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>European Commission</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>€4,000,000 to €8,000,000 per project (Total budget: €40,000,000)</t>
+          <t>Maximum €10,000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Research Infrastructure, Policy Engagement, Technological Framework, Innovation</t>
+          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-DEV-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
+          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
         </is>
       </c>
     </row>
@@ -625,37 +616,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
+          <t>Grant Opportunity: Grants for Developing Internationalisation Strategies for SMEs (Malta)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Private Sector Pathways Program is inviting applications to support innovative small-to-medium enterprises in Queensland to collaborate with corporate partners and develop commercialisation opportunities. The program focuses on increasing partnerships between SMEs and corporate businesses or large organisations to solve problems and trial technologies.</t>
+          <t>The Internationalisation Strategy for SMEs scheme helps SMEs access expert support in developing strategies to improve efficiency, competitiveness, and international market readiness. The scheme supports studying opportunities abroad and developing strategies for selected countries, including marketing and sales plans and risk assessment.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Australian Government (Queensland)</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Up to $100,000</t>
+          <t>Maximum €20,000 per undertaking</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
+          <t>International market readiness, market feasibility, entry strategy, smart economic transformation</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
+          <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
         </is>
       </c>
     </row>
@@ -665,37 +656,37 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
+          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The Cyber Valley AI Incubator offers a practical platform for researchers, technologists, and innovators to develop and launch AI-driven ventures. The program provides a collaborative environment where participants can develop their ideas into tangible ventures, leveraging world-class research and expertise.</t>
+          <t>The Take Your Shot program is an entrepreneurship program inviting applications from young entrepreneurs to develop their business ideas with funding and professional mentorship. The program includes mandatory workshops and a final pitch event where participants can present their ideas to a panel of judges.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Cyber Valley</t>
+          <t>The Bridge Youth Resource Centre</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Not specified (Incubator program with practical platform and expertise)</t>
+          <t>Up to $20,000 (Scholarship/Awards)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
+          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://ai-incubator.is.mpg.de/</t>
+          <t>https://thebridgeyouth.ca/take-your-shot/</t>
         </is>
       </c>
     </row>
@@ -705,37 +696,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
+          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Low Emissions Industry Program supports projects that reduce emissions in mining and manufacturing facilities while strengthening their transition toward a low-carbon future. The program focuses on driving emissions reductions by co-funding projects, future-proofing industrial assets, and maintaining economic resilience.</t>
+          <t>The European Space Agency is seeking applications to develop space-enabled applications that support wetland sustainability and create viable business opportunities. The opportunity supports feasibility studies over a six-month period for early-stage service concepts that respond to real customer needs while demonstrating technical feasibility and commercial potential.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
+          <t>European Space Agency (ESA)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>$500,000 to $10 million</t>
+          <t>Up to €75,000 per activity (75% of total project cost)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
+          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
+          <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
         </is>
       </c>
     </row>
@@ -745,37 +736,37 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
+          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The Waste Minimisation Fund is seeking applications to support innovative projects that reduce waste, improve resource efficiency, and encourage community participation, education, and long-term behaviour change across the Whangārei District. The fund focuses on complementing and enhancing existing waste minimisation programmes and creating new opportunities for reducing waste.</t>
+          <t>The Business Reports for SMEs Grant Scheme offers funding to support SMEs in creating external consultancy reports to improve efficiency, competitiveness, and investment readiness. It provides financial support to contract external expertise needed to generate high-quality business reports that inform strategic decisions and strengthen operational performance.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Whangārei District Council</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
+          <t>Lump sum of €4,000 (80% aid intensity)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
+          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
+          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
         </is>
       </c>
     </row>
@@ -785,37 +776,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
+          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The European Commission is supporting initiatives to develop advanced digital twin technologies that strengthen preparedness, resilience and decision-making in response to the growing security challenges linked to climate and environmental change. The initiative focuses on improving security and preparedness for the Union and creating a more disaster-resilient society in the face of climate change impacts.</t>
+          <t>The Waste Minimisation Fund is seeking applications to support innovative projects that reduce waste, improve resource efficiency, and encourage community participation, education, and long-term behaviour change across the Whangārei District. The fund focuses on complementing and enhancing existing waste minimisation programmes and creating new opportunities for reducing waste.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>European Commission</t>
+          <t>Whangārei District Council</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
+          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
+          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
+          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
         </is>
       </c>
     </row>
@@ -825,37 +816,37 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
+          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The Take Your Shot program is an entrepreneurship program inviting applications from young entrepreneurs to develop their business ideas with funding and professional mentorship. The program includes mandatory workshops and a final pitch event where participants can present their ideas to a panel of judges.</t>
+          <t>The Standards &amp; Awards for SMEs scheme assists small and medium-sized enterprises in strengthening their business operations and attaining prestigious national or international standards and awards. The scheme focuses on enhancing competitiveness and credibility through internationally recognized certifications or national excellence awards.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>The Bridge Youth Resource Centre</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Up to $20,000 (Scholarship/Awards)</t>
+          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
+          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://thebridgeyouth.ca/take-your-shot/</t>
+          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
         </is>
       </c>
     </row>
@@ -865,17 +856,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
+          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The Centre for Aging + Brain Health Innovation is accepting applications for its Fuel program, designed to remove barriers and accelerate innovative solutions that have the potential to transform the aging experience. The program supports start-up companies and healthcare/research organizations in advancing innovations and achieving validation milestones.</t>
+          <t>The Cyber Valley AI Incubator offers a practical platform for researchers, technologists, and innovators to develop and launch AI-driven ventures. The program provides a collaborative environment where participants can develop their ideas into tangible ventures, leveraging world-class research and expertise.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
+          <t>Cyber Valley</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -885,17 +876,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Up to $500,000 CAD</t>
+          <t>Not specified (Incubator program with practical platform and expertise)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Aging, Brain Health, Healthcare Innovation</t>
+          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
+          <t>https://ai-incubator.is.mpg.de/</t>
         </is>
       </c>
     </row>
@@ -905,37 +896,37 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
+          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>The Business Reports for SMEs Grant Scheme offers funding to support SMEs in creating external consultancy reports to improve efficiency, competitiveness, and investment readiness. It provides financial support to contract external expertise needed to generate high-quality business reports that inform strategic decisions and strengthen operational performance.</t>
+          <t>The Low Emissions Industry Program supports projects that reduce emissions in mining and manufacturing facilities while strengthening their transition toward a low-carbon future. The program focuses on driving emissions reductions by co-funding projects, future-proofing industrial assets, and maintaining economic resilience.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Lump sum of €4,000 (80% aid intensity)</t>
+          <t>$500,000 to $10 million</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
+          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
+          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
         </is>
       </c>
     </row>
@@ -945,82 +936,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
+          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The Marketing Strategy for Micro &amp; Small Enterprises scheme supports micro and small businesses in obtaining professional guidance to design marketing strategies that boost their competitiveness and drive business growth. It part-finances costs incurred for external services contracted to deliver a marketing strategy aligned with the enterprise’s objectives.</t>
+          <t>The European Commission is supporting initiatives to develop advanced digital twin technologies that strengthen preparedness, resilience and decision-making in response to the growing security challenges linked to climate and environmental change. The initiative focuses on improving security and preparedness for the Union and creating a more disaster-resilient society in the face of climate change impacts.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maximum €10,000</t>
+          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
+          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>The European Space Agency is seeking applications to develop space-enabled applications that support wetland sustainability and create viable business opportunities. The opportunity supports feasibility studies over a six-month period for early-stage service concepts that respond to real customer needs while demonstrating technical feasibility and commercial potential.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>European Space Agency (ESA)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Up to €75,000 per activity (75% of total project cost)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:H13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/published/02_Grants_Active.xlsx
+++ b/published/02_Grants_Active.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active_Grants" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Active_Grants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,7 +55,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,13 +63,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -435,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -496,37 +505,37 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
+          <t>Grant Opportunity: Grants for Developing Internationalisation Strategies for SMEs (Malta)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The Centre for Aging + Brain Health Innovation is accepting applications for its Fuel program, designed to remove barriers and accelerate innovative solutions that have the potential to transform the aging experience. The program supports start-up companies and healthcare/research organizations in advancing innovations and achieving validation milestones.</t>
+          <t>The Internationalisation Strategy for SMEs scheme helps SMEs access expert support in developing strategies to improve efficiency, competitiveness, and international market readiness. The scheme supports studying opportunities abroad and developing strategies for selected countries, including marketing and sales plans and risk assessment.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Up to $500,000 CAD</t>
+          <t>Maximum €20,000 per undertaking</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Aging, Brain Health, Healthcare Innovation</t>
+          <t>International market readiness, market feasibility, entry strategy, smart economic transformation</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
+          <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
         </is>
       </c>
     </row>
@@ -536,37 +545,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding for Consolidated Research Infrastructure Clusters</t>
+          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The European Commission is advancing efforts to strengthen and streamline its research infrastructure ecosystem by supporting initiatives that improve coordination, accessibility, and policy engagement across large thematic domains. The programme aims to equip large thematic clusters of European research infrastructures with both a policy-oriented and a technical framework to better represent their collective interests and enhance collaboration across the research ecosystem.</t>
+          <t>The Standards &amp; Awards for SMEs scheme assists small and medium-sized enterprises in strengthening their business operations and attaining prestigious national or international standards and awards. The scheme focuses on enhancing competitiveness and credibility through internationally recognized certifications or national excellence awards.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>European Commission</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>€4,000,000 to €8,000,000 per project (Total budget: €40,000,000)</t>
+          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Research Infrastructure, Policy Engagement, Technological Framework, Innovation</t>
+          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-DEV-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
+          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
         </is>
       </c>
     </row>
@@ -576,37 +585,37 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
+          <t>Grant Opportunity: Funding for Consolidated Research Infrastructure Clusters</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>The Marketing Strategy for Micro &amp; Small Enterprises scheme supports micro and small businesses in obtaining professional guidance to design marketing strategies that boost their competitiveness and drive business growth. It part-finances costs incurred for external services contracted to deliver a marketing strategy aligned with the enterprise’s objectives.</t>
+          <t>The European Commission is advancing efforts to strengthen and streamline its research infrastructure ecosystem by supporting initiatives that improve coordination, accessibility, and policy engagement across large thematic domains. The programme aims to equip large thematic clusters of European research infrastructures with both a policy-oriented and a technical framework to better represent their collective interests and enhance collaboration across the research ecosystem.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Maximum €10,000</t>
+          <t>€4,000,000 to €8,000,000 per project (Total budget: €40,000,000)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
+          <t>Research Infrastructure, Policy Engagement, Technological Framework, Innovation</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-DEV-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
         </is>
       </c>
     </row>
@@ -616,37 +625,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Grants for Developing Internationalisation Strategies for SMEs (Malta)</t>
+          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Internationalisation Strategy for SMEs scheme helps SMEs access expert support in developing strategies to improve efficiency, competitiveness, and international market readiness. The scheme supports studying opportunities abroad and developing strategies for selected countries, including marketing and sales plans and risk assessment.</t>
+          <t>The Private Sector Pathways Program is inviting applications to support innovative small-to-medium enterprises in Queensland to collaborate with corporate partners and develop commercialisation opportunities. The program focuses on increasing partnerships between SMEs and corporate businesses or large organisations to solve problems and trial technologies.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>Australian Government (Queensland)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maximum €20,000 per undertaking</t>
+          <t>Up to $100,000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>International market readiness, market feasibility, entry strategy, smart economic transformation</t>
+          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/internationalisation-strategy-for-smes/</t>
+          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
         </is>
       </c>
     </row>
@@ -656,37 +665,37 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
+          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The Take Your Shot program is an entrepreneurship program inviting applications from young entrepreneurs to develop their business ideas with funding and professional mentorship. The program includes mandatory workshops and a final pitch event where participants can present their ideas to a panel of judges.</t>
+          <t>The Cyber Valley AI Incubator offers a practical platform for researchers, technologists, and innovators to develop and launch AI-driven ventures. The program provides a collaborative environment where participants can develop their ideas into tangible ventures, leveraging world-class research and expertise.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>The Bridge Youth Resource Centre</t>
+          <t>Cyber Valley</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Up to $20,000 (Scholarship/Awards)</t>
+          <t>Not specified (Incubator program with practical platform and expertise)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
+          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://thebridgeyouth.ca/take-your-shot/</t>
+          <t>https://ai-incubator.is.mpg.de/</t>
         </is>
       </c>
     </row>
@@ -696,37 +705,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
+          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The European Space Agency is seeking applications to develop space-enabled applications that support wetland sustainability and create viable business opportunities. The opportunity supports feasibility studies over a six-month period for early-stage service concepts that respond to real customer needs while demonstrating technical feasibility and commercial potential.</t>
+          <t>The Low Emissions Industry Program supports projects that reduce emissions in mining and manufacturing facilities while strengthening their transition toward a low-carbon future. The program focuses on driving emissions reductions by co-funding projects, future-proofing industrial assets, and maintaining economic resilience.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>European Space Agency (ESA)</t>
+          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Up to €75,000 per activity (75% of total project cost)</t>
+          <t>$500,000 to $10 million</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
+          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
+          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
         </is>
       </c>
     </row>
@@ -736,37 +745,37 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
+          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The Business Reports for SMEs Grant Scheme offers funding to support SMEs in creating external consultancy reports to improve efficiency, competitiveness, and investment readiness. It provides financial support to contract external expertise needed to generate high-quality business reports that inform strategic decisions and strengthen operational performance.</t>
+          <t>The Waste Minimisation Fund is seeking applications to support innovative projects that reduce waste, improve resource efficiency, and encourage community participation, education, and long-term behaviour change across the Whangārei District. The fund focuses on complementing and enhancing existing waste minimisation programmes and creating new opportunities for reducing waste.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>Whangārei District Council</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Lump sum of €4,000 (80% aid intensity)</t>
+          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
+          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
+          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
         </is>
       </c>
     </row>
@@ -776,37 +785,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
+          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The Waste Minimisation Fund is seeking applications to support innovative projects that reduce waste, improve resource efficiency, and encourage community participation, education, and long-term behaviour change across the Whangārei District. The fund focuses on complementing and enhancing existing waste minimisation programmes and creating new opportunities for reducing waste.</t>
+          <t>The European Commission is supporting initiatives to develop advanced digital twin technologies that strengthen preparedness, resilience and decision-making in response to the growing security challenges linked to climate and environmental change. The initiative focuses on improving security and preparedness for the Union and creating a more disaster-resilient society in the face of climate change impacts.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Whangārei District Council</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
+          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
+          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
         </is>
       </c>
     </row>
@@ -816,37 +825,37 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CFAs: Standards and Awards Support for SMEs (Malta)</t>
+          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The Standards &amp; Awards for SMEs scheme assists small and medium-sized enterprises in strengthening their business operations and attaining prestigious national or international standards and awards. The scheme focuses on enhancing competitiveness and credibility through internationally recognized certifications or national excellence awards.</t>
+          <t>The Take Your Shot program is an entrepreneurship program inviting applications from young entrepreneurs to develop their business ideas with funding and professional mentorship. The program includes mandatory workshops and a final pitch event where participants can present their ideas to a panel of judges.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>The Bridge Youth Resource Centre</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Maximum €15,000 (up to €20,000 for multiple standards)</t>
+          <t>Up to $20,000 (Scholarship/Awards)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Internationally recognized certifications, national excellence awards, quality, efficiency, sustainability</t>
+          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/standards-awards-for-smes/</t>
+          <t>https://thebridgeyouth.ca/take-your-shot/</t>
         </is>
       </c>
     </row>
@@ -856,17 +865,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
+          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The Cyber Valley AI Incubator offers a practical platform for researchers, technologists, and innovators to develop and launch AI-driven ventures. The program provides a collaborative environment where participants can develop their ideas into tangible ventures, leveraging world-class research and expertise.</t>
+          <t>The Centre for Aging + Brain Health Innovation is accepting applications for its Fuel program, designed to remove barriers and accelerate innovative solutions that have the potential to transform the aging experience. The program supports start-up companies and healthcare/research organizations in advancing innovations and achieving validation milestones.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cyber Valley</t>
+          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -876,17 +885,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not specified (Incubator program with practical platform and expertise)</t>
+          <t>Up to $500,000 CAD</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
+          <t>Aging, Brain Health, Healthcare Innovation</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://ai-incubator.is.mpg.de/</t>
+          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
         </is>
       </c>
     </row>
@@ -896,37 +905,37 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
+          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>The Low Emissions Industry Program supports projects that reduce emissions in mining and manufacturing facilities while strengthening their transition toward a low-carbon future. The program focuses on driving emissions reductions by co-funding projects, future-proofing industrial assets, and maintaining economic resilience.</t>
+          <t>The Business Reports for SMEs Grant Scheme offers funding to support SMEs in creating external consultancy reports to improve efficiency, competitiveness, and investment readiness. It provides financial support to contract external expertise needed to generate high-quality business reports that inform strategic decisions and strengthen operational performance.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>$500,000 to $10 million</t>
+          <t>Lump sum of €4,000 (80% aid intensity)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
+          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
+          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
         </is>
       </c>
     </row>
@@ -936,42 +945,82 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
+          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The European Commission is supporting initiatives to develop advanced digital twin technologies that strengthen preparedness, resilience and decision-making in response to the growing security challenges linked to climate and environmental change. The initiative focuses on improving security and preparedness for the Union and creating a more disaster-resilient society in the face of climate change impacts.</t>
+          <t>The Marketing Strategy for Micro &amp; Small Enterprises scheme supports micro and small businesses in obtaining professional guidance to design marketing strategies that boost their competitiveness and drive business growth. It part-finances costs incurred for external services contracted to deliver a marketing strategy aligned with the enterprise’s objectives.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>European Commission</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
+          <t>Maximum €10,000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
+          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
+          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>The European Space Agency is seeking applications to develop space-enabled applications that support wetland sustainability and create viable business opportunities. The opportunity supports feasibility studies over a six-month period for early-stage service concepts that respond to real customer needs while demonstrating technical feasibility and commercial potential.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>European Space Agency (ESA)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Up to €75,000 per activity (75% of total project cost)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/published/02_Grants_Active.xlsx
+++ b/published/02_Grants_Active.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Active_Grants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$H$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -625,37 +625,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Applications open for Private Sector Pathways Program (Australia)</t>
+          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Private Sector Pathways Program is inviting applications to support innovative small-to-medium enterprises in Queensland to collaborate with corporate partners and develop commercialisation opportunities. The program focuses on increasing partnerships between SMEs and corporate businesses or large organisations to solve problems and trial technologies.</t>
+          <t>The Cyber Valley AI Incubator offers a practical platform for researchers, technologists, and innovators to develop and launch AI-driven ventures. The program provides a collaborative environment where participants can develop their ideas into tangible ventures, leveraging world-class research and expertise.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Australian Government (Queensland)</t>
+          <t>Cyber Valley</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Up to $100,000</t>
+          <t>Not specified (Incubator program with practical platform and expertise)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Commercialisation opportunities, SME-Corporate partnerships, advanced manufacturing, hydrogen, biomedical, aerospace</t>
+          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/private-sector-pathways-program-qld</t>
+          <t>https://ai-incubator.is.mpg.de/</t>
         </is>
       </c>
     </row>
@@ -665,37 +665,37 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
+          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The Cyber Valley AI Incubator offers a practical platform for researchers, technologists, and innovators to develop and launch AI-driven ventures. The program provides a collaborative environment where participants can develop their ideas into tangible ventures, leveraging world-class research and expertise.</t>
+          <t>The Low Emissions Industry Program supports projects that reduce emissions in mining and manufacturing facilities while strengthening their transition toward a low-carbon future. The program focuses on driving emissions reductions by co-funding projects, future-proofing industrial assets, and maintaining economic resilience.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Cyber Valley</t>
+          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Not specified (Incubator program with practical platform and expertise)</t>
+          <t>$500,000 to $10 million</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
+          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://ai-incubator.is.mpg.de/</t>
+          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
         </is>
       </c>
     </row>
@@ -705,37 +705,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
+          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Low Emissions Industry Program supports projects that reduce emissions in mining and manufacturing facilities while strengthening their transition toward a low-carbon future. The program focuses on driving emissions reductions by co-funding projects, future-proofing industrial assets, and maintaining economic resilience.</t>
+          <t>The Waste Minimisation Fund is seeking applications to support innovative projects that reduce waste, improve resource efficiency, and encourage community participation, education, and long-term behaviour change across the Whangārei District. The fund focuses on complementing and enhancing existing waste minimisation programmes and creating new opportunities for reducing waste.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
+          <t>Whangārei District Council</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>$500,000 to $10 million</t>
+          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
+          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
+          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
         </is>
       </c>
     </row>
@@ -745,37 +745,37 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
+          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The Waste Minimisation Fund is seeking applications to support innovative projects that reduce waste, improve resource efficiency, and encourage community participation, education, and long-term behaviour change across the Whangārei District. The fund focuses on complementing and enhancing existing waste minimisation programmes and creating new opportunities for reducing waste.</t>
+          <t>The European Commission is supporting initiatives to develop advanced digital twin technologies that strengthen preparedness, resilience and decision-making in response to the growing security challenges linked to climate and environmental change. The initiative focuses on improving security and preparedness for the Union and creating a more disaster-resilient society in the face of climate change impacts.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Whangārei District Council</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
+          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
+          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
         </is>
       </c>
     </row>
@@ -785,37 +785,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
+          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The European Commission is supporting initiatives to develop advanced digital twin technologies that strengthen preparedness, resilience and decision-making in response to the growing security challenges linked to climate and environmental change. The initiative focuses on improving security and preparedness for the Union and creating a more disaster-resilient society in the face of climate change impacts.</t>
+          <t>The Take Your Shot program is an entrepreneurship program inviting applications from young entrepreneurs to develop their business ideas with funding and professional mentorship. The program includes mandatory workshops and a final pitch event where participants can present their ideas to a panel of judges.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>European Commission</t>
+          <t>The Bridge Youth Resource Centre</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
+          <t>Up to $20,000 (Scholarship/Awards)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
+          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
+          <t>https://thebridgeyouth.ca/take-your-shot/</t>
         </is>
       </c>
     </row>
@@ -825,37 +825,37 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
+          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The Take Your Shot program is an entrepreneurship program inviting applications from young entrepreneurs to develop their business ideas with funding and professional mentorship. The program includes mandatory workshops and a final pitch event where participants can present their ideas to a panel of judges.</t>
+          <t>The Centre for Aging + Brain Health Innovation is accepting applications for its Fuel program, designed to remove barriers and accelerate innovative solutions that have the potential to transform the aging experience. The program supports start-up companies and healthcare/research organizations in advancing innovations and achieving validation milestones.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>The Bridge Youth Resource Centre</t>
+          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Up to $20,000 (Scholarship/Awards)</t>
+          <t>Up to $500,000 CAD</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
+          <t>Aging, Brain Health, Healthcare Innovation</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://thebridgeyouth.ca/take-your-shot/</t>
+          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
         </is>
       </c>
     </row>
@@ -865,37 +865,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
+          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The Centre for Aging + Brain Health Innovation is accepting applications for its Fuel program, designed to remove barriers and accelerate innovative solutions that have the potential to transform the aging experience. The program supports start-up companies and healthcare/research organizations in advancing innovations and achieving validation milestones.</t>
+          <t>The Business Reports for SMEs Grant Scheme offers funding to support SMEs in creating external consultancy reports to improve efficiency, competitiveness, and investment readiness. It provides financial support to contract external expertise needed to generate high-quality business reports that inform strategic decisions and strengthen operational performance.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Up to $500,000 CAD</t>
+          <t>Lump sum of €4,000 (80% aid intensity)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Aging, Brain Health, Healthcare Innovation</t>
+          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
+          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
+          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>The Business Reports for SMEs Grant Scheme offers funding to support SMEs in creating external consultancy reports to improve efficiency, competitiveness, and investment readiness. It provides financial support to contract external expertise needed to generate high-quality business reports that inform strategic decisions and strengthen operational performance.</t>
+          <t>The Marketing Strategy for Micro &amp; Small Enterprises scheme supports micro and small businesses in obtaining professional guidance to design marketing strategies that boost their competitiveness and drive business growth. It part-finances costs incurred for external services contracted to deliver a marketing strategy aligned with the enterprise’s objectives.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -925,17 +925,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Lump sum of €4,000 (80% aid intensity)</t>
+          <t>Maximum €10,000</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
+          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
+          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
         </is>
       </c>
     </row>
@@ -945,82 +945,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
+          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The Marketing Strategy for Micro &amp; Small Enterprises scheme supports micro and small businesses in obtaining professional guidance to design marketing strategies that boost their competitiveness and drive business growth. It part-finances costs incurred for external services contracted to deliver a marketing strategy aligned with the enterprise’s objectives.</t>
+          <t>The European Space Agency is seeking applications to develop space-enabled applications that support wetland sustainability and create viable business opportunities. The opportunity supports feasibility studies over a six-month period for early-stage service concepts that respond to real customer needs while demonstrating technical feasibility and commercial potential.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>European Space Agency (ESA)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maximum €10,000</t>
+          <t>Up to €75,000 per activity (75% of total project cost)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
+          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>The European Space Agency is seeking applications to develop space-enabled applications that support wetland sustainability and create viable business opportunities. The opportunity supports feasibility studies over a six-month period for early-stage service concepts that respond to real customer needs while demonstrating technical feasibility and commercial potential.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>European Space Agency (ESA)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Up to €75,000 per activity (75% of total project cost)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
           <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:H13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/published/02_Grants_Active.xlsx
+++ b/published/02_Grants_Active.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Active_Grants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active_Grants'!$A$1:$H$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -625,37 +625,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Entries Open for Cyber Valley AI Incubator Program</t>
+          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Cyber Valley AI Incubator offers a practical platform for researchers, technologists, and innovators to develop and launch AI-driven ventures. The program provides a collaborative environment where participants can develop their ideas into tangible ventures, leveraging world-class research and expertise.</t>
+          <t>The Low Emissions Industry Program supports projects that reduce emissions in mining and manufacturing facilities while strengthening their transition toward a low-carbon future. The program focuses on driving emissions reductions by co-funding projects, future-proofing industrial assets, and maintaining economic resilience.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cyber Valley</t>
+          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Not specified (Incubator program with practical platform and expertise)</t>
+          <t>$500,000 to $10 million</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Artificial Intelligence, Machine Learning, Robotics, Intelligent Systems, Data Science, Biomedical Technology</t>
+          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://ai-incubator.is.mpg.de/</t>
+          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
         </is>
       </c>
     </row>
@@ -665,37 +665,37 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Open Call for Low Emissions Industry Program in Australia</t>
+          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>The Low Emissions Industry Program supports projects that reduce emissions in mining and manufacturing facilities while strengthening their transition toward a low-carbon future. The program focuses on driving emissions reductions by co-funding projects, future-proofing industrial assets, and maintaining economic resilience.</t>
+          <t>The Waste Minimisation Fund is seeking applications to support innovative projects that reduce waste, improve resource efficiency, and encourage community participation, education, and long-term behaviour change across the Whangārei District. The fund focuses on complementing and enhancing existing waste minimisation programmes and creating new opportunities for reducing waste.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Australian Government (Department of Climate Change, Energy, the Environment and Water)</t>
+          <t>Whangārei District Council</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>$500,000 to $10 million</t>
+          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Emissions reduction in mining and manufacturing, transition to net zero</t>
+          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://business.gov.au/grants-and-programs/low-emissions-industry-program-nsw</t>
+          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
         </is>
       </c>
     </row>
@@ -705,37 +705,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Waste Minimisation Fund in New Zealand</t>
+          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Waste Minimisation Fund is seeking applications to support innovative projects that reduce waste, improve resource efficiency, and encourage community participation, education, and long-term behaviour change across the Whangārei District. The fund focuses on complementing and enhancing existing waste minimisation programmes and creating new opportunities for reducing waste.</t>
+          <t>The European Commission is supporting initiatives to develop advanced digital twin technologies that strengthen preparedness, resilience and decision-making in response to the growing security challenges linked to climate and environmental change. The initiative focuses on improving security and preparedness for the Union and creating a more disaster-resilient society in the face of climate change impacts.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Whangārei District Council</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Standard grants ranging from $1,000 to $5,000 and special project grants from $5,000 to $30,000</t>
+          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Waste Minimisation, Resource Efficiency, Community Participation</t>
+          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.wdc.govt.nz/Community/Community-funding/Waste-Minimisation-Fund</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
         </is>
       </c>
     </row>
@@ -745,37 +745,37 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Advancing Digital Twins for Climate, Environment and Security</t>
+          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The European Commission is supporting initiatives to develop advanced digital twin technologies that strengthen preparedness, resilience and decision-making in response to the growing security challenges linked to climate and environmental change. The initiative focuses on improving security and preparedness for the Union and creating a more disaster-resilient society in the face of climate change impacts.</t>
+          <t>The Take Your Shot program is an entrepreneurship program inviting applications from young entrepreneurs to develop their business ideas with funding and professional mentorship. The program includes mandatory workshops and a final pitch event where participants can present their ideas to a panel of judges.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>European Commission</t>
+          <t>The Bridge Youth Resource Centre</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>€5,000,000 to €7,500,000 per project (Total budget: €15,000,000)</t>
+          <t>Up to $20,000 (Scholarship/Awards)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Digital Twins, Climate Change, Environment, Security, AI</t>
+          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/topic-details/HORIZON-INFRA-2026-TECH-01-02?order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate&amp;isExactMatch=true&amp;status=31094502</t>
+          <t>https://thebridgeyouth.ca/take-your-shot/</t>
         </is>
       </c>
     </row>
@@ -785,37 +785,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Take Your Shot Program Entrepreneurship Program (Canada)</t>
+          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The Take Your Shot program is an entrepreneurship program inviting applications from young entrepreneurs to develop their business ideas with funding and professional mentorship. The program includes mandatory workshops and a final pitch event where participants can present their ideas to a panel of judges.</t>
+          <t>The Business Reports for SMEs Grant Scheme offers funding to support SMEs in creating external consultancy reports to improve efficiency, competitiveness, and investment readiness. It provides financial support to contract external expertise needed to generate high-quality business reports that inform strategic decisions and strengthen operational performance.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The Bridge Youth Resource Centre</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Up to $20,000 (Scholarship/Awards)</t>
+          <t>Lump sum of €4,000 (80% aid intensity)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Entrepreneurship, mentorship, workshops, marketing, branding, financial planning</t>
+          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://thebridgeyouth.ca/take-your-shot/</t>
+          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
         </is>
       </c>
     </row>
@@ -825,37 +825,37 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Grant Opportunity: CABHI’s Fuel Program in Canada</t>
+          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The Centre for Aging + Brain Health Innovation is accepting applications for its Fuel program, designed to remove barriers and accelerate innovative solutions that have the potential to transform the aging experience. The program supports start-up companies and healthcare/research organizations in advancing innovations and achieving validation milestones.</t>
+          <t>The Marketing Strategy for Micro &amp; Small Enterprises scheme supports micro and small businesses in obtaining professional guidance to design marketing strategies that boost their competitiveness and drive business growth. It part-finances costs incurred for external services contracted to deliver a marketing strategy aligned with the enterprise’s objectives.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>CABHI (Centre for Aging + Brain Health Innovation)</t>
+          <t>FONDI.eu (Government of Malta)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Up to $500,000 CAD</t>
+          <t>Maximum €10,000</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Aging, Brain Health, Healthcare Innovation</t>
+          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://www.cabhi.com/en/innovation-programs-services/fuel</t>
+          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
         </is>
       </c>
     </row>
@@ -865,122 +865,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grant Opportunity: Funding to Support SMEs’ Business Reports and Plans (Malta)</t>
+          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The Business Reports for SMEs Grant Scheme offers funding to support SMEs in creating external consultancy reports to improve efficiency, competitiveness, and investment readiness. It provides financial support to contract external expertise needed to generate high-quality business reports that inform strategic decisions and strengthen operational performance.</t>
+          <t>The European Space Agency is seeking applications to develop space-enabled applications that support wetland sustainability and create viable business opportunities. The opportunity supports feasibility studies over a six-month period for early-stage service concepts that respond to real customer needs while demonstrating technical feasibility and commercial potential.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FONDI.eu (Government of Malta)</t>
+          <t>European Space Agency (ESA)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lump sum of €4,000 (80% aid intensity)</t>
+          <t>Up to €75,000 per activity (75% of total project cost)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>External consultancy reports, efficiency, competitiveness, investment readiness</t>
+          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://fondi.eu/what-funding-is-available/business-reports-for-smes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Open Call: Marketing Strategy Support Grant for SMEs (Malta)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>The Marketing Strategy for Micro &amp; Small Enterprises scheme supports micro and small businesses in obtaining professional guidance to design marketing strategies that boost their competitiveness and drive business growth. It part-finances costs incurred for external services contracted to deliver a marketing strategy aligned with the enterprise’s objectives.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>FONDI.eu (Government of Malta)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Maximum €10,000</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Marketing strategy, business promotion, competitiveness, smart economic transformation</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>https://fondi.eu/what-funding-is-available/marketing-strategy-for-smes/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Grant Opportunity: Funding Call for Space-Tech Wetland Sustainability Projects</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>The European Space Agency is seeking applications to develop space-enabled applications that support wetland sustainability and create viable business opportunities. The opportunity supports feasibility studies over a six-month period for early-stage service concepts that respond to real customer needs while demonstrating technical feasibility and commercial potential.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>European Space Agency (ESA)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Up to €75,000 per activity (75% of total project cost)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Space-enabled applications for wetland sustainability, water purification, flood control, biodiversity support</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
           <t>https://business.esa.int/funding/call-for-proposals-competitive/sustainable-wetlands</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>